--- a/output/Data and Chart Outputs/thailand_gas.xlsx
+++ b/output/Data and Chart Outputs/thailand_gas.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart - Demand" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Supply" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Demand" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Production by field" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Demand" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -146,13 +148,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -177,10 +179,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -205,10 +207,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -233,10 +235,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -269,8 +271,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -296,8 +298,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -314,7 +316,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -328,7 +330,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -337,13 +339,316 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Thailand gas production by field (EPPO / PTT) (to Jul/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$B$2:$B$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$C$2:$C$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$D$2:$D$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$E$2:$E$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="E87BA4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$F$2:$F$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$G$2:$G$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Production by field'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Production by field'!$A$2:$A$140</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Production by field'!$H$2:$H$140</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="30"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="11"/>
+        <tickMarkSkip val="11"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>mcm/d, monthly average</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,10 +673,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -396,10 +701,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -424,10 +729,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -452,10 +757,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -488,8 +793,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -515,8 +820,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -533,7 +838,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -547,7 +852,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -556,7 +861,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -571,9 +876,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -583,7 +888,34 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -598,9 +930,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -939,7 +1271,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -961,7 +1292,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1016,7 +1346,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1030,7 +1360,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1044,7 +1374,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1058,7 +1388,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1072,7 +1402,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1086,7 +1416,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1100,7 +1430,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1114,7 +1444,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1128,7 +1458,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1142,7 +1472,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1156,7 +1486,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1170,7 +1500,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1184,7 +1514,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1198,7 +1528,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1212,7 +1542,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1226,7 +1556,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1240,7 +1570,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1254,7 +1584,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1268,7 +1598,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1282,7 +1612,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1296,7 +1626,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1310,7 +1640,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1324,7 +1654,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1338,7 +1668,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1352,7 +1682,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1366,7 +1696,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1380,7 +1710,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1394,7 +1724,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1408,7 +1738,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1422,7 +1752,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1436,7 +1766,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1450,7 +1780,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1464,7 +1794,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -1478,7 +1808,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -1492,7 +1822,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -1506,7 +1836,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -1520,7 +1850,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -1534,7 +1864,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -1548,7 +1878,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -1562,7 +1892,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -1576,7 +1906,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -1590,7 +1920,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -1604,7 +1934,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -1618,7 +1948,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -1632,7 +1962,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -1646,7 +1976,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -1660,7 +1990,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -1674,7 +2004,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -1688,7 +2018,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -1702,7 +2032,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -1716,7 +2046,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -1730,7 +2060,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -1744,7 +2074,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -1758,7 +2088,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -1772,7 +2102,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -1786,7 +2116,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -1800,7 +2130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -1814,7 +2144,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -1828,7 +2158,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -1842,7 +2172,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -1856,7 +2186,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -1870,7 +2200,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -1884,7 +2214,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -1898,7 +2228,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -1912,7 +2242,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -1926,7 +2256,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -1940,7 +2270,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -1954,7 +2284,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -1968,7 +2298,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -1982,7 +2312,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -1996,7 +2326,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -2010,7 +2340,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -2024,7 +2354,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -2038,7 +2368,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -2052,7 +2382,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -2066,7 +2396,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -2080,7 +2410,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -2094,7 +2424,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2108,7 +2438,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2122,7 +2452,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2136,7 +2466,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2150,7 +2480,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2164,7 +2494,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2178,7 +2508,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -2192,7 +2522,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -2206,7 +2536,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -2220,7 +2550,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -2234,7 +2564,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -2248,7 +2578,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -2262,7 +2592,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -2276,7 +2606,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -2290,7 +2620,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -2304,7 +2634,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -2318,7 +2648,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -2332,7 +2662,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -2346,7 +2676,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -2360,7 +2690,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -2374,7 +2704,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -2388,7 +2718,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -2402,7 +2732,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -2416,7 +2746,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -2430,7 +2760,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -2444,7 +2774,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -2458,7 +2788,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -2472,7 +2802,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -2486,7 +2816,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -2500,7 +2830,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -2514,7 +2844,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -2528,7 +2858,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -2542,7 +2872,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -2556,7 +2886,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -2570,7 +2900,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -2584,7 +2914,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -2598,7 +2928,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -2612,7 +2942,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -2626,7 +2956,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -2640,7 +2970,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -2654,7 +2984,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -2668,7 +2998,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -2682,7 +3012,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -2696,7 +3026,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -2710,7 +3040,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -2724,7 +3054,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -2738,7 +3068,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -2752,7 +3082,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -2766,7 +3096,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -2780,7 +3110,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -2794,7 +3124,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -2808,7 +3138,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -2822,7 +3152,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -2836,7 +3166,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -2850,7 +3180,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -2864,7 +3194,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -2878,7 +3208,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -2892,7 +3222,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -2906,7 +3236,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -2920,7 +3250,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -2934,7 +3264,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -2948,7 +3278,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -2968,6 +3298,3506 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Erawan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bongkot</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Bongkot Tai</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Arthit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Pailin</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>JDA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Other fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>42005</v>
+      </c>
+      <c r="B2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>42036</v>
+      </c>
+      <c r="B3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>42064</v>
+      </c>
+      <c r="B4" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>42095</v>
+      </c>
+      <c r="B5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>42125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>42156</v>
+      </c>
+      <c r="B7" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>42186</v>
+      </c>
+      <c r="B8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>42217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>42248</v>
+      </c>
+      <c r="B10" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>42278</v>
+      </c>
+      <c r="B11" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>42309</v>
+      </c>
+      <c r="B12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B13" t="n">
+        <v>35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>42370</v>
+      </c>
+      <c r="B14" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>42401</v>
+      </c>
+      <c r="B15" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>42430</v>
+      </c>
+      <c r="B16" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>42461</v>
+      </c>
+      <c r="B17" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>42491</v>
+      </c>
+      <c r="B18" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>42522</v>
+      </c>
+      <c r="B19" t="n">
+        <v>33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="B20" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>42583</v>
+      </c>
+      <c r="B21" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>42614</v>
+      </c>
+      <c r="B22" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>42644</v>
+      </c>
+      <c r="B23" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>42675</v>
+      </c>
+      <c r="B24" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B25" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>42736</v>
+      </c>
+      <c r="B26" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>42767</v>
+      </c>
+      <c r="B27" t="n">
+        <v>36</v>
+      </c>
+      <c r="C27" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>42795</v>
+      </c>
+      <c r="B28" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>42826</v>
+      </c>
+      <c r="B29" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>42856</v>
+      </c>
+      <c r="B30" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>42887</v>
+      </c>
+      <c r="B31" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>42917</v>
+      </c>
+      <c r="B32" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>42948</v>
+      </c>
+      <c r="B33" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>42979</v>
+      </c>
+      <c r="B34" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="B35" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>43040</v>
+      </c>
+      <c r="B36" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>43101</v>
+      </c>
+      <c r="B38" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>43132</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>43160</v>
+      </c>
+      <c r="B40" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>43191</v>
+      </c>
+      <c r="B41" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>43221</v>
+      </c>
+      <c r="B42" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>43252</v>
+      </c>
+      <c r="B43" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43282</v>
+      </c>
+      <c r="B44" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>43313</v>
+      </c>
+      <c r="B45" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>43344</v>
+      </c>
+      <c r="B46" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>43374</v>
+      </c>
+      <c r="B47" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C47" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43405</v>
+      </c>
+      <c r="B48" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B49" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="B50" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="C50" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>43497</v>
+      </c>
+      <c r="B51" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>43525</v>
+      </c>
+      <c r="B52" t="n">
+        <v>38</v>
+      </c>
+      <c r="C52" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>43556</v>
+      </c>
+      <c r="B53" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>43586</v>
+      </c>
+      <c r="B54" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="C54" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>11</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>43617</v>
+      </c>
+      <c r="B55" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="B56" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C56" t="n">
+        <v>15</v>
+      </c>
+      <c r="D56" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>43678</v>
+      </c>
+      <c r="B57" t="n">
+        <v>40</v>
+      </c>
+      <c r="C57" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G57" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>43709</v>
+      </c>
+      <c r="B58" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="C58" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>43739</v>
+      </c>
+      <c r="B59" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>11</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>43770</v>
+      </c>
+      <c r="B60" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>15</v>
+      </c>
+      <c r="H60" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B61" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="B62" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>43862</v>
+      </c>
+      <c r="B63" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>43891</v>
+      </c>
+      <c r="B64" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12</v>
+      </c>
+      <c r="H64" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>43922</v>
+      </c>
+      <c r="B65" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="C65" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H65" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>43952</v>
+      </c>
+      <c r="B66" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>43983</v>
+      </c>
+      <c r="B67" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H67" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B68" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>44044</v>
+      </c>
+      <c r="B69" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>44075</v>
+      </c>
+      <c r="B70" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B71" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>12</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B72" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B73" t="n">
+        <v>30</v>
+      </c>
+      <c r="C73" t="n">
+        <v>15</v>
+      </c>
+      <c r="D73" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B74" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C74" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B75" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C75" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B76" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="C76" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G76" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H76" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B77" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C77" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D77" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B78" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D78" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>13</v>
+      </c>
+      <c r="H78" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B79" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E79" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B80" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C80" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B81" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B82" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G82" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H82" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B83" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C83" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B84" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E84" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B85" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C85" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B86" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D86" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B87" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B88" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C88" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D88" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F88" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H88" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B89" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C90" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E90" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B91" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C91" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D91" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C92" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F92" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B93" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D93" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F93" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B94" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F94" t="n">
+        <v>13</v>
+      </c>
+      <c r="G94" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B95" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C95" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>13</v>
+      </c>
+      <c r="H95" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B96" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+      <c r="D96" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E96" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G96" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H96" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B97" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C97" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12</v>
+      </c>
+      <c r="G97" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B98" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C98" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D98" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B99" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C99" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G99" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B100" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C100" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E100" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F100" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B101" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E101" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F101" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C102" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>11</v>
+      </c>
+      <c r="G102" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B103" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C103" t="n">
+        <v>27</v>
+      </c>
+      <c r="E103" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H103" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B104" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>25</v>
+      </c>
+      <c r="E104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G104" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B105" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C105" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12</v>
+      </c>
+      <c r="G105" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C106" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E106" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H106" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E107" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F107" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G107" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H107" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B108" t="n">
+        <v>11</v>
+      </c>
+      <c r="C108" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E108" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B109" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C109" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F109" t="n">
+        <v>12</v>
+      </c>
+      <c r="G109" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="C110" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E110" t="n">
+        <v>11</v>
+      </c>
+      <c r="F110" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G110" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B111" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C111" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E111" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F111" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G111" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B112" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C112" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E112" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F112" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G112" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B113" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C113" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>9</v>
+      </c>
+      <c r="F113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G113" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B114" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C114" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E114" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B115" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G115" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H115" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B116" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E116" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G116" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B117" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C117" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E117" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F117" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B118" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C118" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H118" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B119" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E119" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F119" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H119" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B120" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C120" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E120" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B121" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C121" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E121" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G121" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B122" t="n">
+        <v>19</v>
+      </c>
+      <c r="C122" t="n">
+        <v>21</v>
+      </c>
+      <c r="E122" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G122" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B123" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E123" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F123" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G123" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C124" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G124" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B125" t="n">
+        <v>23</v>
+      </c>
+      <c r="C125" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>11</v>
+      </c>
+      <c r="G125" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B126" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C126" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F126" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B127" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C127" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F127" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>9</v>
+      </c>
+      <c r="H127" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B128" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C128" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>11</v>
+      </c>
+      <c r="H128" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B129" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C129" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E129" t="n">
+        <v>10</v>
+      </c>
+      <c r="F129" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B130" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C130" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G130" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B131" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C131" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F131" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H131" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B132" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C132" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>12</v>
+      </c>
+      <c r="G132" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H132" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B133" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C133" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B134" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="C134" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F134" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B135" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>11</v>
+      </c>
+      <c r="F135" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B136" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C136" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G136" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B137" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C137" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E137" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F137" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G137" t="n">
+        <v>8</v>
+      </c>
+      <c r="H137" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B138" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C138" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E138" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>8</v>
+      </c>
+      <c r="H138" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B139" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C139" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G139" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B140" t="n">
+        <v>25</v>
+      </c>
+      <c r="C140" t="n">
+        <v>24</v>
+      </c>
+      <c r="E140" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3007,7 +6837,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -3024,7 +6854,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -3041,7 +6871,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -3058,7 +6888,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -3075,7 +6905,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -3092,7 +6922,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -3109,7 +6939,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -3126,7 +6956,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -3143,7 +6973,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -3160,7 +6990,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -3177,7 +7007,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -3194,7 +7024,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -3211,7 +7041,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -3228,7 +7058,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -3245,7 +7075,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -3262,7 +7092,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -3279,7 +7109,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -3296,7 +7126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -3313,7 +7143,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -3330,7 +7160,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -3347,7 +7177,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -3364,7 +7194,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3381,7 +7211,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3398,7 +7228,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3415,7 +7245,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3432,7 +7262,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3449,7 +7279,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -3466,7 +7296,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -3483,7 +7313,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -3500,7 +7330,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -3517,7 +7347,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -3534,7 +7364,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -3551,7 +7381,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -3568,7 +7398,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -3585,7 +7415,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -3602,7 +7432,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -3619,7 +7449,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -3636,7 +7466,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -3653,7 +7483,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -3670,7 +7500,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -3687,7 +7517,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -3704,7 +7534,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -3721,7 +7551,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -3738,7 +7568,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -3755,7 +7585,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -3772,7 +7602,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -3789,7 +7619,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -3806,7 +7636,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -3823,7 +7653,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -3840,7 +7670,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -3857,7 +7687,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -3874,7 +7704,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -3891,7 +7721,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -3908,7 +7738,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -3925,7 +7755,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -3942,7 +7772,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -3959,7 +7789,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -3976,7 +7806,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -3993,7 +7823,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -4010,7 +7840,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -4027,7 +7857,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -4044,7 +7874,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -4061,7 +7891,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -4078,7 +7908,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -4095,7 +7925,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -4112,7 +7942,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -4129,7 +7959,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -4146,7 +7976,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -4163,7 +7993,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -4180,7 +8010,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -4197,7 +8027,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -4214,7 +8044,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -4231,7 +8061,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -4248,7 +8078,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -4265,7 +8095,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -4282,7 +8112,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -4299,7 +8129,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -4316,7 +8146,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -4333,7 +8163,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -4350,7 +8180,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -4367,7 +8197,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -4384,7 +8214,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -4401,7 +8231,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -4418,7 +8248,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -4435,7 +8265,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -4452,7 +8282,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -4469,7 +8299,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -4486,7 +8316,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -4503,7 +8333,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -4520,7 +8350,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -4537,7 +8367,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -4554,7 +8384,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -4571,7 +8401,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -4588,7 +8418,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -4605,7 +8435,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -4622,7 +8452,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -4639,7 +8469,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -4656,7 +8486,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -4673,7 +8503,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -4690,7 +8520,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -4707,7 +8537,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -4724,7 +8554,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -4741,7 +8571,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -4758,7 +8588,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -4775,7 +8605,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -4792,7 +8622,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -4809,7 +8639,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -4826,7 +8656,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -4843,7 +8673,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -4860,7 +8690,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -4877,7 +8707,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -4894,7 +8724,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -4911,7 +8741,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -4928,7 +8758,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -4945,7 +8775,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -4962,7 +8792,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -4979,7 +8809,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -4996,7 +8826,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -5013,7 +8843,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -5030,7 +8860,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -5047,7 +8877,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -5064,7 +8894,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -5081,7 +8911,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -5098,7 +8928,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -5115,7 +8945,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -5132,7 +8962,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -5149,7 +8979,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -5166,7 +8996,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -5183,7 +9013,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -5200,7 +9030,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -5217,7 +9047,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -5234,7 +9064,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -5251,7 +9081,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -5268,7 +9098,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -5285,7 +9115,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -5302,7 +9132,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -5319,7 +9149,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -5336,7 +9166,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -5353,7 +9183,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -5375,7 +9205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27513,7 +31343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/Data and Chart Outputs/thailand_gas.xlsx
+++ b/output/Data and Chart Outputs/thailand_gas.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Production by field" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Demand" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Production by field" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - Demand" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Supply" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -148,13 +147,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -179,10 +178,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -207,10 +206,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -235,10 +234,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -271,8 +270,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -298,8 +297,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -316,7 +315,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -330,7 +329,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -339,13 +338,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -370,10 +369,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -398,10 +397,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -426,10 +425,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -454,10 +453,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -482,10 +481,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -510,10 +509,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -538,10 +537,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -574,8 +573,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -601,8 +600,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -619,7 +618,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -633,7 +632,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -642,13 +641,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -673,10 +672,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -701,10 +700,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -729,10 +728,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -757,10 +756,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -793,8 +792,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -820,8 +819,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -838,7 +837,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -852,7 +851,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -861,7 +860,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -876,9 +875,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -888,7 +887,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -903,9 +902,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -915,7 +914,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -930,9 +929,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1271,6 +1270,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1292,6 +1292,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1346,7 +1347,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1360,7 +1361,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1374,7 +1375,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1388,7 +1389,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1402,7 +1403,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1416,7 +1417,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1430,7 +1431,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1444,7 +1445,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1458,7 +1459,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1472,7 +1473,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1486,7 +1487,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1500,7 +1501,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1514,7 +1515,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1528,7 +1529,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1542,7 +1543,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1556,7 +1557,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1570,7 +1571,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1584,7 +1585,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1598,7 +1599,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1612,7 +1613,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1626,7 +1627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1640,7 +1641,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1654,7 +1655,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1668,7 +1669,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1682,7 +1683,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1696,7 +1697,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1710,7 +1711,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1724,7 +1725,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1738,7 +1739,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1752,7 +1753,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1766,7 +1767,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1780,7 +1781,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1794,7 +1795,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -1808,7 +1809,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -1836,7 +1837,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -1850,7 +1851,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -1864,7 +1865,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -1878,7 +1879,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -1892,7 +1893,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -1906,7 +1907,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -1920,7 +1921,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -1934,7 +1935,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -1948,7 +1949,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -1962,7 +1963,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -1976,7 +1977,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -1990,7 +1991,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -2004,7 +2005,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -2018,7 +2019,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -2032,7 +2033,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -2060,7 +2061,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -2074,7 +2075,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -2088,7 +2089,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -2102,7 +2103,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -2116,7 +2117,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -2130,7 +2131,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -2144,7 +2145,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -2158,7 +2159,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -2172,7 +2173,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -2186,7 +2187,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -2200,7 +2201,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -2214,7 +2215,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -2228,7 +2229,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -2242,7 +2243,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -2256,7 +2257,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -2270,7 +2271,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -2284,7 +2285,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -2298,7 +2299,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -2312,7 +2313,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -2326,7 +2327,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -2340,7 +2341,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -2354,7 +2355,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -2368,7 +2369,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -2382,7 +2383,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -2396,7 +2397,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -2410,7 +2411,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -2424,7 +2425,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2438,7 +2439,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2452,7 +2453,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2466,7 +2467,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2480,7 +2481,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2494,7 +2495,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2508,7 +2509,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -2522,7 +2523,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -2536,7 +2537,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -2550,7 +2551,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -2564,7 +2565,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -2578,7 +2579,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -2592,7 +2593,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -2606,7 +2607,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -2620,7 +2621,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -2634,7 +2635,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -2648,7 +2649,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -2662,7 +2663,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -2676,7 +2677,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -2690,7 +2691,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -2704,7 +2705,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -2718,7 +2719,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -2732,7 +2733,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -2746,7 +2747,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -2760,7 +2761,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -2774,7 +2775,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -2788,7 +2789,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -2802,7 +2803,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -2816,7 +2817,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -2830,7 +2831,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -2844,7 +2845,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -2858,7 +2859,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -2872,7 +2873,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -2886,7 +2887,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -2900,7 +2901,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -2914,7 +2915,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -2928,7 +2929,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -2942,7 +2943,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -2956,7 +2957,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -2970,7 +2971,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -2984,7 +2985,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -2998,7 +2999,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -3012,7 +3013,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -3026,7 +3027,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -3040,7 +3041,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -3054,7 +3055,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -3068,7 +3069,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3082,7 +3083,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3096,7 +3097,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3110,7 +3111,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3124,7 +3125,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3138,7 +3139,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3152,7 +3153,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3166,7 +3167,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3180,7 +3181,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3194,7 +3195,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3208,7 +3209,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3222,7 +3223,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3236,7 +3237,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3250,7 +3251,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3264,7 +3265,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3278,7 +3279,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -3352,7 +3353,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -3375,7 +3376,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -3398,7 +3399,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -3421,7 +3422,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -3444,7 +3445,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -3467,7 +3468,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -3490,7 +3491,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -3513,7 +3514,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -3536,7 +3537,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -3559,7 +3560,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -3582,7 +3583,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -3605,7 +3606,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -3628,7 +3629,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -3651,7 +3652,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -3674,7 +3675,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -3697,7 +3698,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -3720,7 +3721,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -3743,7 +3744,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -3766,7 +3767,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -3792,7 +3793,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -3818,7 +3819,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -3844,7 +3845,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3896,7 +3897,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3922,7 +3923,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3948,7 +3949,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3974,7 +3975,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -4000,7 +4001,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -4026,7 +4027,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -4052,7 +4053,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -4078,7 +4079,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -4104,7 +4105,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -4130,7 +4131,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -4156,7 +4157,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -4182,7 +4183,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -4208,7 +4209,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -4234,7 +4235,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -4260,7 +4261,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -4286,7 +4287,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -4312,7 +4313,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -4338,7 +4339,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -4364,7 +4365,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -4390,7 +4391,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -4416,7 +4417,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -4442,7 +4443,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -4468,7 +4469,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -4494,7 +4495,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -4520,7 +4521,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -4546,7 +4547,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -4572,7 +4573,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -4598,7 +4599,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -4624,7 +4625,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -4650,7 +4651,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -4676,7 +4677,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -4702,7 +4703,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -4728,7 +4729,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -4754,7 +4755,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -4780,7 +4781,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -4806,7 +4807,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -4832,7 +4833,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -4858,7 +4859,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -4884,7 +4885,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -4910,7 +4911,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -4936,7 +4937,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -4962,7 +4963,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -4988,7 +4989,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -5014,7 +5015,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -5040,7 +5041,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -5066,7 +5067,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -5092,7 +5093,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -5118,7 +5119,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -5144,7 +5145,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -5170,7 +5171,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -5196,7 +5197,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -5222,7 +5223,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -5248,7 +5249,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -5274,7 +5275,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -5300,7 +5301,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -5326,7 +5327,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -5352,7 +5353,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -5378,7 +5379,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -5404,7 +5405,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -5430,7 +5431,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -5456,7 +5457,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -5482,7 +5483,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -5508,7 +5509,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -5534,7 +5535,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -5560,7 +5561,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -5586,7 +5587,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -5612,7 +5613,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -5638,7 +5639,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -5664,7 +5665,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -5690,7 +5691,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -5716,7 +5717,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -5742,7 +5743,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -5768,7 +5769,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -5794,7 +5795,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -5820,7 +5821,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5846,7 +5847,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -5872,7 +5873,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -5895,7 +5896,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -5918,7 +5919,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -5941,7 +5942,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -5964,7 +5965,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -5987,7 +5988,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -6010,7 +6011,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -6033,7 +6034,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -6056,7 +6057,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -6079,7 +6080,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -6102,7 +6103,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -6125,7 +6126,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -6148,7 +6149,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -6171,7 +6172,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -6194,7 +6195,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -6217,7 +6218,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -6240,7 +6241,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -6263,7 +6264,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -6286,7 +6287,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -6309,7 +6310,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -6332,7 +6333,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -6355,7 +6356,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -6378,7 +6379,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -6401,7 +6402,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -6424,7 +6425,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -6447,7 +6448,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -6470,7 +6471,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -6493,7 +6494,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -6516,7 +6517,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -6539,7 +6540,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -6562,7 +6563,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -6585,7 +6586,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -6608,7 +6609,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -6631,7 +6632,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -6654,7 +6655,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -6677,7 +6678,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -6700,7 +6701,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -6723,7 +6724,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -6746,7 +6747,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -6769,7 +6770,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -6837,7 +6838,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -6854,7 +6855,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -6871,7 +6872,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -6888,7 +6889,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -6905,7 +6906,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -6922,7 +6923,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -6939,7 +6940,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -6956,7 +6957,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -6973,7 +6974,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -6990,7 +6991,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -7007,7 +7008,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -7024,7 +7025,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -7041,7 +7042,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -7058,7 +7059,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -7075,7 +7076,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -7092,7 +7093,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -7109,7 +7110,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -7126,7 +7127,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -7143,7 +7144,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -7160,7 +7161,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -7177,7 +7178,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -7194,7 +7195,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -7211,7 +7212,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -7228,7 +7229,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -7245,7 +7246,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -7262,7 +7263,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -7279,7 +7280,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -7296,7 +7297,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -7313,7 +7314,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -7330,7 +7331,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -7347,7 +7348,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -7364,7 +7365,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -7381,7 +7382,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -7398,7 +7399,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -7415,7 +7416,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -7432,7 +7433,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -7449,7 +7450,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -7466,7 +7467,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -7483,7 +7484,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -7500,7 +7501,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -7517,7 +7518,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -7534,7 +7535,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -7551,7 +7552,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -7568,7 +7569,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -7585,7 +7586,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -7602,7 +7603,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -7619,7 +7620,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -7636,7 +7637,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -7653,7 +7654,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -7670,7 +7671,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -7687,7 +7688,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -7704,7 +7705,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -7721,7 +7722,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -7738,7 +7739,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -7755,7 +7756,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -7772,7 +7773,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -7789,7 +7790,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -7806,7 +7807,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -7823,7 +7824,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -7840,7 +7841,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -7857,7 +7858,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -7874,7 +7875,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -7891,7 +7892,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -7908,7 +7909,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -7925,7 +7926,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -7942,7 +7943,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -7959,7 +7960,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -7976,7 +7977,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -7993,7 +7994,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -8010,7 +8011,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -8027,7 +8028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -8044,7 +8045,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -8061,7 +8062,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -8078,7 +8079,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -8095,7 +8096,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -8112,7 +8113,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -8129,7 +8130,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -8146,7 +8147,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -8163,7 +8164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -8180,7 +8181,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -8197,7 +8198,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -8214,7 +8215,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -8231,7 +8232,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -8248,7 +8249,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -8265,7 +8266,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -8282,7 +8283,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -8299,7 +8300,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -8316,7 +8317,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -8333,7 +8334,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -8350,7 +8351,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -8367,7 +8368,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -8384,7 +8385,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -8401,7 +8402,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -8418,7 +8419,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -8435,7 +8436,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -8452,7 +8453,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -8469,7 +8470,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -8486,7 +8487,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -8503,7 +8504,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -8520,7 +8521,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -8537,7 +8538,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -8554,7 +8555,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -8571,7 +8572,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -8588,7 +8589,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -8605,7 +8606,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -8622,7 +8623,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -8639,7 +8640,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -8656,7 +8657,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -8673,7 +8674,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -8690,7 +8691,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -8707,7 +8708,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -8724,7 +8725,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -8741,7 +8742,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -8758,7 +8759,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -8775,7 +8776,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -8792,7 +8793,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -8809,7 +8810,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -8826,7 +8827,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -8843,7 +8844,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -8860,7 +8861,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -8877,7 +8878,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -8894,7 +8895,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -8911,7 +8912,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -8928,7 +8929,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -8945,7 +8946,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -8962,7 +8963,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -8979,7 +8980,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -8996,7 +8997,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -9013,7 +9014,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -9030,7 +9031,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -9047,7 +9048,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -9064,7 +9065,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -9081,7 +9082,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -9098,7 +9099,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -9115,7 +9116,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -9132,7 +9133,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -9149,7 +9150,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -9166,7 +9167,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -9183,7 +9184,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">

--- a/output/Data and Chart Outputs/thailand_gas.xlsx
+++ b/output/Data and Chart Outputs/thailand_gas.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1270,7 +1271,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1292,7 +1292,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1347,7 +1346,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1361,7 +1360,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1375,7 +1374,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1389,7 +1388,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1403,7 +1402,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1417,7 +1416,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1431,7 +1430,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1445,7 +1444,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1459,7 +1458,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1473,7 +1472,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1487,7 +1486,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1501,7 +1500,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1515,7 +1514,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1529,7 +1528,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1543,7 +1542,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1557,7 +1556,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1571,7 +1570,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1585,7 +1584,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1599,7 +1598,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1613,7 +1612,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1627,7 +1626,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1641,7 +1640,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1655,7 +1654,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1669,7 +1668,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1683,7 +1682,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1697,7 +1696,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1711,7 +1710,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1725,7 +1724,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1739,7 +1738,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1753,7 +1752,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1767,7 +1766,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1781,7 +1780,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1795,7 +1794,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -1809,7 +1808,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -1837,7 +1836,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -1851,7 +1850,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -1865,7 +1864,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -1879,7 +1878,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -1893,7 +1892,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -1907,7 +1906,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -1921,7 +1920,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -1935,7 +1934,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -1949,7 +1948,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -1963,7 +1962,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -1977,7 +1976,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -1991,7 +1990,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -2005,7 +2004,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -2019,7 +2018,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -2033,7 +2032,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -2047,7 +2046,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -2061,7 +2060,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -2075,7 +2074,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -2089,7 +2088,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -2103,7 +2102,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -2117,7 +2116,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -2131,7 +2130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -2145,7 +2144,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -2159,7 +2158,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -2173,7 +2172,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -2187,7 +2186,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -2201,7 +2200,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -2215,7 +2214,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -2229,7 +2228,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -2243,7 +2242,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -2257,7 +2256,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -2271,7 +2270,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -2285,7 +2284,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -2299,7 +2298,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -2313,7 +2312,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -2327,7 +2326,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -2341,7 +2340,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -2355,7 +2354,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -2369,7 +2368,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -2383,7 +2382,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -2397,7 +2396,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -2411,7 +2410,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -2425,7 +2424,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2439,7 +2438,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2453,7 +2452,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2467,7 +2466,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2481,7 +2480,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2495,7 +2494,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2509,7 +2508,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -2523,7 +2522,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -2537,7 +2536,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -2551,7 +2550,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -2565,7 +2564,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -2579,7 +2578,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -2593,7 +2592,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -2607,7 +2606,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -2621,7 +2620,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -2635,7 +2634,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -2649,7 +2648,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -2663,7 +2662,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -2677,7 +2676,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -2691,7 +2690,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -2705,7 +2704,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -2719,7 +2718,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -2733,7 +2732,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -2747,7 +2746,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -2761,7 +2760,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -2775,7 +2774,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -2789,7 +2788,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -2803,7 +2802,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -2817,7 +2816,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -2831,7 +2830,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -2845,7 +2844,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -2859,7 +2858,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -2873,7 +2872,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -2887,7 +2886,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -2901,7 +2900,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -2915,7 +2914,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -2929,7 +2928,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -2943,7 +2942,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -2957,7 +2956,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -2971,7 +2970,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -2985,7 +2984,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -2999,7 +2998,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -3013,7 +3012,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -3027,7 +3026,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -3041,7 +3040,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -3055,7 +3054,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -3069,7 +3068,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3083,7 +3082,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3097,7 +3096,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3111,7 +3110,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3125,7 +3124,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3139,7 +3138,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3153,7 +3152,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3167,7 +3166,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3181,7 +3180,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3195,7 +3194,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3209,7 +3208,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3223,7 +3222,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3237,7 +3236,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3251,7 +3250,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3265,7 +3264,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3279,7 +3278,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -3353,7 +3352,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -3376,7 +3375,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -3399,7 +3398,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -3422,7 +3421,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -3445,7 +3444,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -3468,7 +3467,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -3491,7 +3490,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -3514,7 +3513,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -3537,7 +3536,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -3560,7 +3559,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -3583,7 +3582,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -3606,7 +3605,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -3629,7 +3628,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -3652,7 +3651,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -3675,7 +3674,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -3698,7 +3697,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -3721,7 +3720,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -3744,7 +3743,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -3767,7 +3766,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -3793,7 +3792,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -3819,7 +3818,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -3845,7 +3844,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3871,7 +3870,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3897,7 +3896,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3923,7 +3922,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3949,7 +3948,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3975,7 +3974,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -4001,7 +4000,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -4027,7 +4026,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -4053,7 +4052,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -4079,7 +4078,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -4105,7 +4104,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -4131,7 +4130,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -4157,7 +4156,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -4183,7 +4182,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -4209,7 +4208,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -4235,7 +4234,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -4261,7 +4260,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -4287,7 +4286,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -4313,7 +4312,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -4339,7 +4338,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -4365,7 +4364,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -4391,7 +4390,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -4417,7 +4416,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -4443,7 +4442,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -4469,7 +4468,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -4495,7 +4494,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -4521,7 +4520,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -4547,7 +4546,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -4573,7 +4572,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -4599,7 +4598,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -4625,7 +4624,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -4651,7 +4650,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -4677,7 +4676,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -4703,7 +4702,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -4729,7 +4728,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -4755,7 +4754,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -4781,7 +4780,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -4807,7 +4806,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -4833,7 +4832,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -4859,7 +4858,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -4885,7 +4884,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -4911,7 +4910,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -4937,7 +4936,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -4963,7 +4962,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -4989,7 +4988,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -5015,7 +5014,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -5041,7 +5040,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -5067,7 +5066,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -5093,7 +5092,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -5119,7 +5118,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -5145,7 +5144,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -5171,7 +5170,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -5197,7 +5196,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -5223,7 +5222,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -5249,7 +5248,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -5275,7 +5274,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -5301,7 +5300,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -5327,7 +5326,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -5353,7 +5352,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -5379,7 +5378,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -5405,7 +5404,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -5431,7 +5430,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -5457,7 +5456,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -5483,7 +5482,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -5509,7 +5508,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -5535,7 +5534,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -5561,7 +5560,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -5587,7 +5586,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -5613,7 +5612,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -5639,7 +5638,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -5665,7 +5664,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -5691,7 +5690,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -5717,7 +5716,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -5743,7 +5742,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -5769,7 +5768,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -5795,7 +5794,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -5821,7 +5820,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5847,7 +5846,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -5873,7 +5872,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -5896,7 +5895,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -5919,7 +5918,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -5942,7 +5941,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -5965,7 +5964,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -5988,7 +5987,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -6011,7 +6010,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -6034,7 +6033,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -6057,7 +6056,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -6080,7 +6079,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -6103,7 +6102,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -6126,7 +6125,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -6149,7 +6148,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -6172,7 +6171,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -6195,7 +6194,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -6218,7 +6217,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -6241,7 +6240,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -6264,7 +6263,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -6287,7 +6286,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -6310,7 +6309,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -6333,7 +6332,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -6356,7 +6355,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -6379,7 +6378,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -6402,7 +6401,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -6425,7 +6424,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -6448,7 +6447,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -6471,7 +6470,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -6494,7 +6493,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -6517,7 +6516,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -6540,7 +6539,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -6563,7 +6562,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -6586,7 +6585,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -6609,7 +6608,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -6632,7 +6631,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -6655,7 +6654,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -6678,7 +6677,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -6701,7 +6700,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -6724,7 +6723,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -6747,7 +6746,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -6770,7 +6769,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -6838,7 +6837,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -6855,7 +6854,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -6872,7 +6871,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -6889,7 +6888,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -6906,7 +6905,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -6923,7 +6922,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -6940,7 +6939,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -6957,7 +6956,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -6974,7 +6973,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -6991,7 +6990,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -7008,7 +7007,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -7025,7 +7024,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -7042,7 +7041,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -7059,7 +7058,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -7076,7 +7075,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -7093,7 +7092,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -7110,7 +7109,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -7127,7 +7126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -7144,7 +7143,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -7161,7 +7160,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -7178,7 +7177,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -7195,7 +7194,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -7212,7 +7211,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -7229,7 +7228,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -7246,7 +7245,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -7263,7 +7262,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -7280,7 +7279,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -7297,7 +7296,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -7314,7 +7313,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -7331,7 +7330,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -7348,7 +7347,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -7365,7 +7364,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -7382,7 +7381,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -7399,7 +7398,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -7416,7 +7415,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -7433,7 +7432,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -7450,7 +7449,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -7467,7 +7466,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -7484,7 +7483,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -7501,7 +7500,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -7518,7 +7517,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -7535,7 +7534,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -7552,7 +7551,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -7569,7 +7568,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -7586,7 +7585,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -7603,7 +7602,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -7620,7 +7619,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -7637,7 +7636,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -7654,7 +7653,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -7671,7 +7670,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -7688,7 +7687,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -7705,7 +7704,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -7722,7 +7721,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -7739,7 +7738,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -7756,7 +7755,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -7773,7 +7772,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -7790,7 +7789,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -7807,7 +7806,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -7824,7 +7823,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -7841,7 +7840,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -7858,7 +7857,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -7875,7 +7874,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -7892,7 +7891,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -7909,7 +7908,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -7926,7 +7925,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -7943,7 +7942,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -7960,7 +7959,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -7977,7 +7976,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -7994,7 +7993,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -8011,7 +8010,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -8028,7 +8027,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -8045,7 +8044,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -8062,7 +8061,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -8079,7 +8078,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -8096,7 +8095,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -8113,7 +8112,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -8130,7 +8129,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -8147,7 +8146,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -8164,7 +8163,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -8181,7 +8180,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -8198,7 +8197,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -8215,7 +8214,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -8232,7 +8231,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -8249,7 +8248,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -8266,7 +8265,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -8283,7 +8282,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -8300,7 +8299,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -8317,7 +8316,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -8334,7 +8333,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -8351,7 +8350,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -8368,7 +8367,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -8385,7 +8384,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -8402,7 +8401,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -8419,7 +8418,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -8436,7 +8435,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -8453,7 +8452,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -8470,7 +8469,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -8487,7 +8486,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -8504,7 +8503,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -8521,7 +8520,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -8538,7 +8537,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -8555,7 +8554,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -8572,7 +8571,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -8589,7 +8588,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -8606,7 +8605,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -8623,7 +8622,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -8640,7 +8639,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -8657,7 +8656,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -8674,7 +8673,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -8691,7 +8690,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -8708,7 +8707,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -8725,7 +8724,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -8742,7 +8741,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -8759,7 +8758,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -8776,7 +8775,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -8793,7 +8792,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -8810,7 +8809,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -8827,7 +8826,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -8844,7 +8843,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -8861,7 +8860,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -8878,7 +8877,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -8895,7 +8894,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -8912,7 +8911,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -8929,7 +8928,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -8946,7 +8945,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -8963,7 +8962,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -8980,7 +8979,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -8997,7 +8996,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -9014,7 +9013,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -9031,7 +9030,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -9048,7 +9047,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -9065,7 +9064,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -9082,7 +9081,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -9099,7 +9098,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -9116,7 +9115,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -9133,7 +9132,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -9150,7 +9149,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -9167,7 +9166,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -9184,7 +9183,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">

--- a/output/Data and Chart Outputs/thailand_gas.xlsx
+++ b/output/Data and Chart Outputs/thailand_gas.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1271,6 +1270,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1292,6 +1292,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1346,7 +1347,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1360,7 +1361,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1374,7 +1375,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1388,7 +1389,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1402,7 +1403,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1416,7 +1417,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1430,7 +1431,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1444,7 +1445,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1458,7 +1459,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1472,7 +1473,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1486,7 +1487,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1500,7 +1501,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1514,7 +1515,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1528,7 +1529,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1542,7 +1543,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1556,7 +1557,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1570,7 +1571,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1584,7 +1585,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1598,7 +1599,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1612,7 +1613,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1626,7 +1627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1640,7 +1641,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1654,7 +1655,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1668,7 +1669,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1682,7 +1683,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1696,7 +1697,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1710,7 +1711,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1724,7 +1725,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1738,7 +1739,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1752,7 +1753,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1766,7 +1767,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1780,7 +1781,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1794,7 +1795,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -1808,7 +1809,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -1836,7 +1837,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -1850,7 +1851,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -1864,7 +1865,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -1878,7 +1879,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -1892,7 +1893,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -1906,7 +1907,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -1920,7 +1921,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -1934,7 +1935,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -1948,7 +1949,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -1962,7 +1963,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -1976,7 +1977,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -1990,7 +1991,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -2004,7 +2005,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -2018,7 +2019,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -2032,7 +2033,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -2060,7 +2061,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -2074,7 +2075,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -2088,7 +2089,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -2102,7 +2103,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -2116,7 +2117,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -2130,7 +2131,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -2144,7 +2145,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -2158,7 +2159,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -2172,7 +2173,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -2186,7 +2187,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -2200,7 +2201,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -2214,7 +2215,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -2228,7 +2229,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -2242,7 +2243,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -2256,7 +2257,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -2270,7 +2271,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -2284,7 +2285,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -2298,7 +2299,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -2312,7 +2313,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -2326,7 +2327,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -2340,7 +2341,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -2354,7 +2355,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -2368,7 +2369,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -2382,7 +2383,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -2396,7 +2397,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -2410,7 +2411,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -2424,7 +2425,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2438,7 +2439,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2452,7 +2453,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2466,7 +2467,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2480,7 +2481,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2494,7 +2495,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2508,7 +2509,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -2522,7 +2523,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -2536,7 +2537,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -2550,7 +2551,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -2564,7 +2565,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -2578,7 +2579,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -2592,7 +2593,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -2606,7 +2607,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -2620,7 +2621,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -2634,7 +2635,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -2648,7 +2649,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -2662,7 +2663,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -2676,7 +2677,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -2690,7 +2691,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -2704,7 +2705,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -2718,7 +2719,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -2732,7 +2733,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -2746,7 +2747,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -2760,7 +2761,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -2774,7 +2775,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -2788,7 +2789,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -2802,7 +2803,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -2816,7 +2817,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -2830,7 +2831,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -2844,7 +2845,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -2858,7 +2859,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -2872,7 +2873,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -2886,7 +2887,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -2900,7 +2901,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -2914,7 +2915,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -2928,7 +2929,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -2942,7 +2943,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -2956,7 +2957,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -2970,7 +2971,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -2984,7 +2985,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -2998,7 +2999,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -3012,7 +3013,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -3026,7 +3027,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -3040,7 +3041,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -3054,7 +3055,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -3068,7 +3069,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3082,7 +3083,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3096,7 +3097,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3110,7 +3111,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3124,7 +3125,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3138,7 +3139,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3152,7 +3153,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3166,7 +3167,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3180,7 +3181,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3194,7 +3195,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3208,7 +3209,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3222,7 +3223,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3236,7 +3237,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3250,7 +3251,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3264,7 +3265,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3278,7 +3279,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -3352,7 +3353,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -3375,7 +3376,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -3398,7 +3399,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -3421,7 +3422,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -3444,7 +3445,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -3467,7 +3468,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -3490,7 +3491,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -3513,7 +3514,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -3536,7 +3537,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -3559,7 +3560,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -3582,7 +3583,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -3605,7 +3606,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -3628,7 +3629,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -3651,7 +3652,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -3674,7 +3675,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -3697,7 +3698,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -3720,7 +3721,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -3743,7 +3744,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -3766,7 +3767,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -3792,7 +3793,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -3818,7 +3819,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -3844,7 +3845,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3896,7 +3897,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3922,7 +3923,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3948,7 +3949,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3974,7 +3975,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -4000,7 +4001,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -4026,7 +4027,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -4052,7 +4053,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -4078,7 +4079,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -4104,7 +4105,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -4130,7 +4131,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -4156,7 +4157,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -4182,7 +4183,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -4208,7 +4209,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -4234,7 +4235,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -4260,7 +4261,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -4286,7 +4287,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -4312,7 +4313,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -4338,7 +4339,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -4364,7 +4365,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -4390,7 +4391,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -4416,7 +4417,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -4442,7 +4443,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -4468,7 +4469,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -4494,7 +4495,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -4520,7 +4521,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -4546,7 +4547,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -4572,7 +4573,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -4598,7 +4599,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -4624,7 +4625,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -4650,7 +4651,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -4676,7 +4677,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -4702,7 +4703,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -4728,7 +4729,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -4754,7 +4755,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -4780,7 +4781,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -4806,7 +4807,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -4832,7 +4833,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -4858,7 +4859,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -4884,7 +4885,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -4910,7 +4911,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -4936,7 +4937,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -4962,7 +4963,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -4988,7 +4989,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -5014,7 +5015,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -5040,7 +5041,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -5066,7 +5067,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -5092,7 +5093,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -5118,7 +5119,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -5144,7 +5145,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -5170,7 +5171,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -5196,7 +5197,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -5222,7 +5223,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -5248,7 +5249,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -5274,7 +5275,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -5300,7 +5301,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -5326,7 +5327,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -5352,7 +5353,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -5378,7 +5379,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -5404,7 +5405,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -5430,7 +5431,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -5456,7 +5457,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -5482,7 +5483,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -5508,7 +5509,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -5534,7 +5535,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -5560,7 +5561,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -5586,7 +5587,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -5612,7 +5613,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -5638,7 +5639,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -5664,7 +5665,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -5690,7 +5691,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -5716,7 +5717,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -5742,7 +5743,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -5768,7 +5769,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -5794,7 +5795,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -5820,7 +5821,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5846,7 +5847,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -5872,7 +5873,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -5895,7 +5896,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -5918,7 +5919,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -5941,7 +5942,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -5964,7 +5965,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -5987,7 +5988,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -6010,7 +6011,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -6033,7 +6034,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -6056,7 +6057,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -6079,7 +6080,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -6102,7 +6103,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -6125,7 +6126,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -6148,7 +6149,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -6171,7 +6172,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -6194,7 +6195,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -6217,7 +6218,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -6240,7 +6241,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -6263,7 +6264,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -6286,7 +6287,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -6309,7 +6310,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -6332,7 +6333,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -6355,7 +6356,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -6378,7 +6379,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -6401,7 +6402,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -6424,7 +6425,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -6447,7 +6448,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -6470,7 +6471,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -6493,7 +6494,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -6516,7 +6517,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -6539,7 +6540,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -6562,7 +6563,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -6585,7 +6586,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -6608,7 +6609,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -6631,7 +6632,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -6654,7 +6655,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -6677,7 +6678,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -6700,7 +6701,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -6723,7 +6724,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -6746,7 +6747,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -6769,7 +6770,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
@@ -6837,7 +6838,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -6854,7 +6855,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -6871,7 +6872,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -6888,7 +6889,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -6905,7 +6906,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -6922,7 +6923,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -6939,7 +6940,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -6956,7 +6957,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -6973,7 +6974,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -6990,7 +6991,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -7007,7 +7008,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -7024,7 +7025,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -7041,7 +7042,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -7058,7 +7059,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -7075,7 +7076,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -7092,7 +7093,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -7109,7 +7110,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -7126,7 +7127,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -7143,7 +7144,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -7160,7 +7161,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -7177,7 +7178,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -7194,7 +7195,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -7211,7 +7212,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -7228,7 +7229,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -7245,7 +7246,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -7262,7 +7263,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -7279,7 +7280,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -7296,7 +7297,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -7313,7 +7314,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -7330,7 +7331,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -7347,7 +7348,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -7364,7 +7365,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -7381,7 +7382,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -7398,7 +7399,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -7415,7 +7416,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -7432,7 +7433,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -7449,7 +7450,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -7466,7 +7467,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -7483,7 +7484,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -7500,7 +7501,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -7517,7 +7518,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -7534,7 +7535,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -7551,7 +7552,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -7568,7 +7569,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -7585,7 +7586,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -7602,7 +7603,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -7619,7 +7620,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -7636,7 +7637,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -7653,7 +7654,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -7670,7 +7671,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -7687,7 +7688,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -7704,7 +7705,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -7721,7 +7722,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -7738,7 +7739,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -7755,7 +7756,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -7772,7 +7773,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -7789,7 +7790,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -7806,7 +7807,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -7823,7 +7824,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -7840,7 +7841,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -7857,7 +7858,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -7874,7 +7875,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -7891,7 +7892,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -7908,7 +7909,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -7925,7 +7926,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -7942,7 +7943,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -7959,7 +7960,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -7976,7 +7977,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -7993,7 +7994,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -8010,7 +8011,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -8027,7 +8028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -8044,7 +8045,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -8061,7 +8062,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -8078,7 +8079,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -8095,7 +8096,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -8112,7 +8113,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -8129,7 +8130,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -8146,7 +8147,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -8163,7 +8164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -8180,7 +8181,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -8197,7 +8198,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -8214,7 +8215,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -8231,7 +8232,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -8248,7 +8249,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -8265,7 +8266,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -8282,7 +8283,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -8299,7 +8300,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -8316,7 +8317,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -8333,7 +8334,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -8350,7 +8351,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -8367,7 +8368,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -8384,7 +8385,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -8401,7 +8402,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -8418,7 +8419,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -8435,7 +8436,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -8452,7 +8453,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -8469,7 +8470,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -8486,7 +8487,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -8503,7 +8504,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -8520,7 +8521,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -8537,7 +8538,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -8554,7 +8555,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -8571,7 +8572,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -8588,7 +8589,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -8605,7 +8606,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -8622,7 +8623,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -8639,7 +8640,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -8656,7 +8657,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -8673,7 +8674,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -8690,7 +8691,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -8707,7 +8708,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -8724,7 +8725,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -8741,7 +8742,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -8758,7 +8759,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -8775,7 +8776,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -8792,7 +8793,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -8809,7 +8810,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -8826,7 +8827,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -8843,7 +8844,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -8860,7 +8861,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -8877,7 +8878,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -8894,7 +8895,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -8911,7 +8912,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -8928,7 +8929,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -8945,7 +8946,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -8962,7 +8963,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -8979,7 +8980,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -8996,7 +8997,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -9013,7 +9014,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -9030,7 +9031,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -9047,7 +9048,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -9064,7 +9065,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -9081,7 +9082,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -9098,7 +9099,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -9115,7 +9116,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -9132,7 +9133,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -9149,7 +9150,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -9166,7 +9167,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -9183,7 +9184,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">

--- a/output/Data and Chart Outputs/thailand_gas.xlsx
+++ b/output/Data and Chart Outputs/thailand_gas.xlsx
@@ -158,7 +158,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Thailand gas supply: domestic, Myanmar pipeline and LNG (EPPO / PTT) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Thailand gas supply: domestic, Myanmar pipeline and LNG (EPPO / PTT) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$140</f>
+              <f>'Chart'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$140</f>
+              <f>'Chart'!$B$2:$B$141</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$140</f>
+              <f>'Chart'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$140</f>
+              <f>'Chart'!$C$2:$C$141</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$140</f>
+              <f>'Chart'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$140</f>
+              <f>'Chart'!$D$2:$D$141</f>
             </numRef>
           </val>
         </ser>
@@ -349,7 +350,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Thailand gas production by field (EPPO / PTT) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Thailand gas production by field (EPPO / PTT) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -379,12 +381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$B$2:$B$140</f>
+              <f>'Chart - Production by field'!$B$2:$B$141</f>
             </numRef>
           </val>
         </ser>
@@ -407,12 +409,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$C$2:$C$140</f>
+              <f>'Chart - Production by field'!$C$2:$C$141</f>
             </numRef>
           </val>
         </ser>
@@ -435,12 +437,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$D$2:$D$140</f>
+              <f>'Chart - Production by field'!$D$2:$D$141</f>
             </numRef>
           </val>
         </ser>
@@ -463,12 +465,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$E$2:$E$140</f>
+              <f>'Chart - Production by field'!$E$2:$E$141</f>
             </numRef>
           </val>
         </ser>
@@ -491,12 +493,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$F$2:$F$140</f>
+              <f>'Chart - Production by field'!$F$2:$F$141</f>
             </numRef>
           </val>
         </ser>
@@ -519,12 +521,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$G$2:$G$140</f>
+              <f>'Chart - Production by field'!$G$2:$G$141</f>
             </numRef>
           </val>
         </ser>
@@ -538,7 +540,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -547,12 +549,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Production by field'!$A$2:$A$140</f>
+              <f>'Chart - Production by field'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production by field'!$H$2:$H$140</f>
+              <f>'Chart - Production by field'!$H$2:$H$141</f>
             </numRef>
           </val>
         </ser>
@@ -652,7 +654,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Thailand gas consumption by sector (EPPO / PTT) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Thailand gas consumption by sector (EPPO / PTT) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -682,12 +685,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$140</f>
+              <f>'Chart - Demand'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$B$2:$B$140</f>
+              <f>'Chart - Demand'!$B$2:$B$141</f>
             </numRef>
           </val>
         </ser>
@@ -710,12 +713,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$140</f>
+              <f>'Chart - Demand'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$C$2:$C$140</f>
+              <f>'Chart - Demand'!$C$2:$C$141</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +741,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$140</f>
+              <f>'Chart - Demand'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$D$2:$D$140</f>
+              <f>'Chart - Demand'!$D$2:$D$141</f>
             </numRef>
           </val>
         </ser>
@@ -766,12 +769,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$140</f>
+              <f>'Chart - Demand'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$E$2:$E$140</f>
+              <f>'Chart - Demand'!$E$2:$E$141</f>
             </numRef>
           </val>
         </ser>
@@ -1281,14 +1284,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supply monthly 1986-01..2026-07; demand monthly 1986-01..2026-07. EPPO updates about two months after the month.</t>
+          <t>Supply monthly 1986-01..2026-08; demand monthly 1986-01..2026-08. EPPO updates about two months after the month.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Files read this run: T03_01_01-1.xls (Last-Modified Mon, 14 Sep 2026 09:28:57 GMT); T03_01_01.xls (Last-Modified Mon, 14 Sep 2026 09:28:52 GMT); T03_02_02-1.xls (Last-Modified Mon, 14 Sep 2026 09:29:21 GMT); T03_02_02.xls (Last-Modified Mon, 14 Sep 2026 09:29:17 GMT)</t>
+          <t>Files read this run: T03_01_01-1.xls (Last-Modified Mon, 14 Sep 2026 09:28:57 GMT); T03_01_01.xls (Last-Modified Sat, 17 Oct 2026 10:20:09 GMT); T03_02_02-1.xls (Last-Modified Mon, 14 Sep 2026 09:29:21 GMT); T03_02_02.xls (Last-Modified Sat, 17 Oct 2026 10:20:15 GMT)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3290,6 +3293,20 @@
       </c>
       <c r="D140" t="n">
         <v>52.2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B141" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="C141" t="n">
+        <v>12</v>
+      </c>
+      <c r="D141" t="n">
+        <v>32.6</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6789,6 +6806,29 @@
         <v>7.3</v>
       </c>
       <c r="H140" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B141" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E141" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F141" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H141" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -6804,7 +6844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9198,6 +9238,23 @@
       </c>
       <c r="E140" t="n">
         <v>2.1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B141" t="n">
+        <v>86</v>
+      </c>
+      <c r="C141" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D141" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9212,7 +9269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W488"/>
+  <dimension ref="A1:W489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29394,9 +29451,6 @@
       <c r="L458" t="n">
         <v>6</v>
       </c>
-      <c r="M458" t="n">
-        <v>0</v>
-      </c>
       <c r="N458" t="n">
         <v>430</v>
       </c>
@@ -29459,9 +29513,6 @@
       <c r="L459" t="n">
         <v>5</v>
       </c>
-      <c r="M459" t="n">
-        <v>0</v>
-      </c>
       <c r="N459" t="n">
         <v>427</v>
       </c>
@@ -29524,9 +29575,6 @@
       <c r="L460" t="n">
         <v>6</v>
       </c>
-      <c r="M460" t="n">
-        <v>0</v>
-      </c>
       <c r="N460" t="n">
         <v>430</v>
       </c>
@@ -29589,9 +29637,6 @@
       <c r="L461" t="n">
         <v>5</v>
       </c>
-      <c r="M461" t="n">
-        <v>0</v>
-      </c>
       <c r="N461" t="n">
         <v>414</v>
       </c>
@@ -29914,9 +29959,6 @@
       <c r="L466" t="n">
         <v>8</v>
       </c>
-      <c r="M466" t="n">
-        <v>0</v>
-      </c>
       <c r="N466" t="n">
         <v>412</v>
       </c>
@@ -30044,9 +30086,6 @@
       <c r="L468" t="n">
         <v>7</v>
       </c>
-      <c r="M468" t="n">
-        <v>0</v>
-      </c>
       <c r="N468" t="n">
         <v>485</v>
       </c>
@@ -30109,9 +30148,6 @@
       <c r="L469" t="n">
         <v>8</v>
       </c>
-      <c r="M469" t="n">
-        <v>0</v>
-      </c>
       <c r="N469" t="n">
         <v>447</v>
       </c>
@@ -30174,9 +30210,6 @@
       <c r="L470" t="n">
         <v>10</v>
       </c>
-      <c r="M470" t="n">
-        <v>0</v>
-      </c>
       <c r="N470" t="n">
         <v>452</v>
       </c>
@@ -30363,9 +30396,6 @@
       <c r="L473" t="n">
         <v>6</v>
       </c>
-      <c r="M473" t="n">
-        <v>0</v>
-      </c>
       <c r="N473" t="n">
         <v>327</v>
       </c>
@@ -30676,9 +30706,6 @@
       <c r="L478" t="n">
         <v>6</v>
       </c>
-      <c r="M478" t="n">
-        <v>0</v>
-      </c>
       <c r="N478" t="n">
         <v>329</v>
       </c>
@@ -30741,9 +30768,6 @@
       <c r="L479" t="n">
         <v>7</v>
       </c>
-      <c r="M479" t="n">
-        <v>0</v>
-      </c>
       <c r="N479" t="n">
         <v>305</v>
       </c>
@@ -30868,9 +30892,6 @@
       <c r="L481" t="n">
         <v>6</v>
       </c>
-      <c r="M481" t="n">
-        <v>0</v>
-      </c>
       <c r="N481" t="n">
         <v>360</v>
       </c>
@@ -31119,9 +31140,6 @@
       <c r="L485" t="n">
         <v>4</v>
       </c>
-      <c r="M485" t="n">
-        <v>0</v>
-      </c>
       <c r="N485" t="n">
         <v>283</v>
       </c>
@@ -31337,6 +31355,68 @@
       </c>
       <c r="W488" t="n">
         <v>419</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B489" t="n">
+        <v>816</v>
+      </c>
+      <c r="C489" t="n">
+        <v>739</v>
+      </c>
+      <c r="E489" t="n">
+        <v>406</v>
+      </c>
+      <c r="F489" t="n">
+        <v>402</v>
+      </c>
+      <c r="G489" t="n">
+        <v>84</v>
+      </c>
+      <c r="H489" t="n">
+        <v>106</v>
+      </c>
+      <c r="I489" t="n">
+        <v>20</v>
+      </c>
+      <c r="K489" t="n">
+        <v>5</v>
+      </c>
+      <c r="L489" t="n">
+        <v>3</v>
+      </c>
+      <c r="N489" t="n">
+        <v>285</v>
+      </c>
+      <c r="O489" t="n">
+        <v>20</v>
+      </c>
+      <c r="P489" t="n">
+        <v>2887</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>152</v>
+      </c>
+      <c r="R489" t="n">
+        <v>29</v>
+      </c>
+      <c r="S489" t="n">
+        <v>243</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1152</v>
+      </c>
+      <c r="U489" t="n">
+        <v>1576</v>
+      </c>
+      <c r="V489" t="n">
+        <v>4463</v>
+      </c>
+      <c r="W489" t="n">
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -31350,7 +31430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I488"/>
+  <dimension ref="A1:I489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44008,6 +44088,35 @@
         <v>4752</v>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B489" t="n">
+        <v>819</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D489" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E489" t="n">
+        <v>3038</v>
+      </c>
+      <c r="F489" t="n">
+        <v>753</v>
+      </c>
+      <c r="G489" t="n">
+        <v>907</v>
+      </c>
+      <c r="H489" t="n">
+        <v>71</v>
+      </c>
+      <c r="I489" t="n">
+        <v>4768</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
